--- a/docentes/Moreno Aroyo Anél - Estadisticos 20232.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -82,31 +82,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
     <t>LEONEL</t>
-  </si>
-  <si>
-    <t>IAN</t>
   </si>
 </sst>
 </file>
@@ -702,16 +684,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -725,16 +710,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>92.31</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -748,16 +736,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>83.87</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -771,16 +762,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -794,16 +788,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -817,16 +814,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H7">
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -882,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -917,7 +917,7 @@
         <v>92.31</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -934,16 +934,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>77.42</v>
+        <v>83.87</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>77.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>54.17</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1012,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>86.84</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1063,16 +1063,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920034</v>
+        <v>23330051920037</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1081,52 +1081,6 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920037</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920043</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20232.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -82,13 +82,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>OMAR DAVID</t>
+  </si>
+  <si>
+    <t>IRVING</t>
   </si>
 </sst>
 </file>
@@ -882,16 +891,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -934,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>83.87</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -960,16 +969,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>85.70999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -986,16 +995,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1031,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1063,24 +1072,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920037</v>
+        <v>23330051920005</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920028</v>
+      </c>
+      <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Moreno Aroyo Anél - Estadisticos 20232.xlsx
+++ b/docentes/Moreno Aroyo Anél - Estadisticos 20232.xlsx
@@ -82,22 +82,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CAMPOS</t>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>RIVERA</t>
+    <t>IRVING</t>
   </si>
   <si>
     <t>OMAR DAVID</t>
-  </si>
-  <si>
-    <t>IRVING</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920005</v>
+        <v>23330051920028</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1087,7 +1087,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920028</v>
+        <v>23330051920005</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1110,10 +1110,10 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
